--- a/data/misc/skip_conditions_final.xlsx
+++ b/data/misc/skip_conditions_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Desktop/CES Accuracy Analysis/data/misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84421227-AD40-FA46-9657-3E6BD3070817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4C10A0-F1B0-5445-A81C-F9CBE01F2245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="1560" windowWidth="17000" windowHeight="12740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1840" yWindow="1560" windowWidth="23080" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="67">
   <si>
     <t>State</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>SENATOR_rc</t>
+  </si>
+  <si>
+    <t>Secretary of State does not have these election results tabulated</t>
   </si>
 </sst>
 </file>
@@ -573,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1108,16 +1111,16 @@
         <v>14</v>
       </c>
       <c r="B32">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1125,16 +1128,16 @@
         <v>14</v>
       </c>
       <c r="B33">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1142,16 +1145,16 @@
         <v>14</v>
       </c>
       <c r="B34">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1159,21 +1162,21 @@
         <v>14</v>
       </c>
       <c r="B35">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35" t="b">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>2012</v>
@@ -1190,7 +1193,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37">
         <v>2012</v>
@@ -1207,7 +1210,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>2016</v>
@@ -1224,7 +1227,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>2016</v>
@@ -1241,7 +1244,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>2012</v>
@@ -1258,7 +1261,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41">
         <v>2012</v>
@@ -1275,7 +1278,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42">
         <v>2016</v>
@@ -1292,7 +1295,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43">
         <v>2016</v>
@@ -1309,7 +1312,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>2012</v>
@@ -1326,7 +1329,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B45">
         <v>2012</v>
@@ -1343,7 +1346,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46">
         <v>2016</v>
@@ -1360,7 +1363,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B47">
         <v>2016</v>
@@ -1377,13 +1380,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B48">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" t="b">
         <v>1</v>
@@ -1394,13 +1397,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49">
         <v>2012</v>
       </c>
       <c r="C49" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49" t="b">
         <v>1</v>
@@ -1411,13 +1414,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B50">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" t="b">
         <v>1</v>
@@ -1428,10 +1431,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B51">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -1448,10 +1451,10 @@
         <v>18</v>
       </c>
       <c r="B52">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D52" t="b">
         <v>1</v>
@@ -1465,10 +1468,10 @@
         <v>18</v>
       </c>
       <c r="B53">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53" t="b">
         <v>1</v>
@@ -1479,27 +1482,27 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B54">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B55">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
@@ -1508,32 +1511,32 @@
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B56">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B57">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
@@ -1542,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1550,10 +1553,10 @@
         <v>19</v>
       </c>
       <c r="B58">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
@@ -1570,7 +1573,7 @@
         <v>2010</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
@@ -1587,7 +1590,7 @@
         <v>2012</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D60" t="b">
         <v>1</v>
@@ -1601,10 +1604,10 @@
         <v>19</v>
       </c>
       <c r="B61">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D61" t="b">
         <v>1</v>
@@ -1618,10 +1621,10 @@
         <v>19</v>
       </c>
       <c r="B62">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
@@ -1635,10 +1638,10 @@
         <v>19</v>
       </c>
       <c r="B63">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
@@ -1652,10 +1655,10 @@
         <v>19</v>
       </c>
       <c r="B64">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="D64" t="b">
         <v>1</v>
@@ -1669,10 +1672,10 @@
         <v>19</v>
       </c>
       <c r="B65">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="D65" t="b">
         <v>1</v>
@@ -1686,10 +1689,10 @@
         <v>19</v>
       </c>
       <c r="B66">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C66" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D66" t="b">
         <v>1</v>
@@ -1703,7 +1706,7 @@
         <v>19</v>
       </c>
       <c r="B67">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C67" t="s">
         <v>65</v>
@@ -1720,7 +1723,7 @@
         <v>19</v>
       </c>
       <c r="B68">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="C68" t="s">
         <v>65</v>
@@ -1737,7 +1740,7 @@
         <v>19</v>
       </c>
       <c r="B69">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C69" t="s">
         <v>65</v>
@@ -1754,7 +1757,7 @@
         <v>19</v>
       </c>
       <c r="B70">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C70" t="s">
         <v>65</v>
@@ -1771,7 +1774,7 @@
         <v>19</v>
       </c>
       <c r="B71">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C71" t="s">
         <v>65</v>
@@ -1785,13 +1788,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D72" t="b">
         <v>1</v>
@@ -1802,13 +1805,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C73" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D73" t="b">
         <v>1</v>
@@ -1819,30 +1822,30 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B74">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C74" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C75" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D75" t="b">
         <v>1</v>
@@ -1856,7 +1859,7 @@
         <v>20</v>
       </c>
       <c r="B76">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
@@ -1873,16 +1876,16 @@
         <v>20</v>
       </c>
       <c r="B77">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D77" t="b">
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -1890,41 +1893,41 @@
         <v>20</v>
       </c>
       <c r="B78">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B79">
         <v>2012</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D79" t="b">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B80">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C80" t="s">
         <v>10</v>
@@ -1933,12 +1936,12 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B81">
         <v>2016</v>
@@ -1955,7 +1958,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B82">
         <v>2016</v>
@@ -1967,15 +1970,15 @@
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B83">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
@@ -1984,32 +1987,32 @@
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B84">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B85">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
@@ -2018,24 +2021,24 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B86">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C86" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -2043,7 +2046,7 @@
         <v>22</v>
       </c>
       <c r="B87">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
@@ -2060,10 +2063,10 @@
         <v>22</v>
       </c>
       <c r="B88">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D88" t="b">
         <v>1</v>
@@ -2077,10 +2080,10 @@
         <v>22</v>
       </c>
       <c r="B89">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D89" t="b">
         <v>1</v>
@@ -2094,10 +2097,10 @@
         <v>22</v>
       </c>
       <c r="B90">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D90" t="b">
         <v>1</v>
@@ -2111,10 +2114,10 @@
         <v>22</v>
       </c>
       <c r="B91">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D91" t="b">
         <v>1</v>
@@ -2128,7 +2131,7 @@
         <v>22</v>
       </c>
       <c r="B92">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C92" t="s">
         <v>10</v>
@@ -2142,27 +2145,27 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B93">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C93" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D93" t="b">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B94">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
@@ -2171,29 +2174,29 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B95">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D95" t="b">
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B96">
         <v>2016</v>
@@ -2205,12 +2208,12 @@
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B97">
         <v>2012</v>
@@ -2227,7 +2230,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B98">
         <v>2012</v>
@@ -2244,7 +2247,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99">
         <v>2016</v>
@@ -2261,7 +2264,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B100">
         <v>2016</v>
@@ -2278,10 +2281,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B101">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
@@ -2295,7 +2298,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B102">
         <v>2012</v>
@@ -2312,10 +2315,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B103">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C103" t="s">
         <v>9</v>
@@ -2329,7 +2332,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B104">
         <v>2016</v>
@@ -2349,7 +2352,7 @@
         <v>25</v>
       </c>
       <c r="B105">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="C105" t="s">
         <v>9</v>
@@ -2363,13 +2366,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B106">
         <v>2012</v>
       </c>
       <c r="C106" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D106" t="b">
         <v>1</v>
@@ -2380,13 +2383,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B107">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D107" t="b">
         <v>1</v>
@@ -2397,13 +2400,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B108">
         <v>2016</v>
       </c>
       <c r="C108" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D108" t="b">
         <v>1</v>
@@ -2414,13 +2417,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B109">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D109" t="b">
         <v>1</v>
@@ -2431,7 +2434,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B110">
         <v>2012</v>
@@ -2448,7 +2451,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B111">
         <v>2012</v>
@@ -2465,7 +2468,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B112">
         <v>2016</v>
@@ -2482,7 +2485,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B113">
         <v>2016</v>
@@ -2499,10 +2502,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B114">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C114" t="s">
         <v>9</v>
@@ -2516,10 +2519,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B115">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C115" t="s">
         <v>10</v>
@@ -2533,10 +2536,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B116">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C116" t="s">
         <v>9</v>
@@ -2550,10 +2553,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B117">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C117" t="s">
         <v>10</v>
@@ -2570,7 +2573,7 @@
         <v>28</v>
       </c>
       <c r="B118">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C118" t="s">
         <v>9</v>
@@ -2587,7 +2590,7 @@
         <v>28</v>
       </c>
       <c r="B119">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C119" t="s">
         <v>10</v>
@@ -2604,7 +2607,7 @@
         <v>28</v>
       </c>
       <c r="B120">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C120" t="s">
         <v>9</v>
@@ -2621,7 +2624,7 @@
         <v>28</v>
       </c>
       <c r="B121">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C121" t="s">
         <v>10</v>
@@ -2638,7 +2641,7 @@
         <v>28</v>
       </c>
       <c r="B122">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C122" t="s">
         <v>9</v>
@@ -2655,7 +2658,7 @@
         <v>28</v>
       </c>
       <c r="B123">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
@@ -2669,13 +2672,13 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B124">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C124" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D124" t="b">
         <v>1</v>
@@ -2686,13 +2689,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B125">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C125" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D125" t="b">
         <v>1</v>
@@ -2703,10 +2706,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B126">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C126" t="s">
         <v>9</v>
@@ -2720,10 +2723,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B127">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C127" t="s">
         <v>10</v>
@@ -2740,7 +2743,7 @@
         <v>29</v>
       </c>
       <c r="B128">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C128" t="s">
         <v>6</v>
@@ -2757,7 +2760,7 @@
         <v>29</v>
       </c>
       <c r="B129">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C129" t="s">
         <v>8</v>
@@ -2774,7 +2777,7 @@
         <v>29</v>
       </c>
       <c r="B130">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C130" t="s">
         <v>9</v>
@@ -2791,7 +2794,7 @@
         <v>29</v>
       </c>
       <c r="B131">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C131" t="s">
         <v>10</v>
@@ -2808,7 +2811,7 @@
         <v>29</v>
       </c>
       <c r="B132">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C132" t="s">
         <v>6</v>
@@ -2825,7 +2828,7 @@
         <v>29</v>
       </c>
       <c r="B133">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C133" t="s">
         <v>8</v>
@@ -2842,7 +2845,7 @@
         <v>29</v>
       </c>
       <c r="B134">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C134" t="s">
         <v>9</v>
@@ -2859,7 +2862,7 @@
         <v>29</v>
       </c>
       <c r="B135">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C135" t="s">
         <v>10</v>
@@ -2876,7 +2879,7 @@
         <v>29</v>
       </c>
       <c r="B136">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C136" t="s">
         <v>6</v>
@@ -2893,7 +2896,7 @@
         <v>29</v>
       </c>
       <c r="B137">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -2910,7 +2913,7 @@
         <v>29</v>
       </c>
       <c r="B138">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C138" t="s">
         <v>9</v>
@@ -2927,7 +2930,7 @@
         <v>29</v>
       </c>
       <c r="B139">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C139" t="s">
         <v>10</v>
@@ -2944,7 +2947,7 @@
         <v>29</v>
       </c>
       <c r="B140">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C140" t="s">
         <v>6</v>
@@ -2961,7 +2964,7 @@
         <v>29</v>
       </c>
       <c r="B141">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C141" t="s">
         <v>8</v>
@@ -2978,10 +2981,10 @@
         <v>29</v>
       </c>
       <c r="B142">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C142" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D142" t="b">
         <v>1</v>
@@ -2995,10 +2998,10 @@
         <v>29</v>
       </c>
       <c r="B143">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C143" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D143" t="b">
         <v>1</v>
@@ -3012,10 +3015,10 @@
         <v>29</v>
       </c>
       <c r="B144">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C144" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D144" t="b">
         <v>1</v>
@@ -3029,10 +3032,10 @@
         <v>29</v>
       </c>
       <c r="B145">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C145" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D145" t="b">
         <v>1</v>
@@ -3046,7 +3049,7 @@
         <v>29</v>
       </c>
       <c r="B146">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C146" t="s">
         <v>8</v>
@@ -3060,70 +3063,70 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B147">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C147" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D147" t="b">
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B148">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C148" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D148" t="b">
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B149">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C149" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D149" t="b">
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B150">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C150" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D150" t="b">
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -3131,7 +3134,7 @@
         <v>30</v>
       </c>
       <c r="B151">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C151" t="s">
         <v>9</v>
@@ -3148,7 +3151,7 @@
         <v>30</v>
       </c>
       <c r="B152">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C152" t="s">
         <v>10</v>
@@ -3165,7 +3168,7 @@
         <v>30</v>
       </c>
       <c r="B153">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C153" t="s">
         <v>9</v>
@@ -3182,7 +3185,7 @@
         <v>30</v>
       </c>
       <c r="B154">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C154" t="s">
         <v>10</v>
@@ -3199,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="B155">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C155" t="s">
         <v>9</v>
@@ -3216,7 +3219,7 @@
         <v>30</v>
       </c>
       <c r="B156">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C156" t="s">
         <v>10</v>
@@ -3230,13 +3233,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B157">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C157" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D157" t="b">
         <v>1</v>
@@ -3247,44 +3250,44 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B158">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C158" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D158" t="b">
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B159">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C159" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D159" t="b">
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B160">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C160" t="s">
         <v>10</v>
@@ -3301,16 +3304,16 @@
         <v>31</v>
       </c>
       <c r="B161">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C161" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D161" t="b">
         <v>1</v>
       </c>
       <c r="E161" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -3318,16 +3321,16 @@
         <v>31</v>
       </c>
       <c r="B162">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C162" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D162" t="b">
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -3335,10 +3338,10 @@
         <v>31</v>
       </c>
       <c r="B163">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C163" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D163" t="b">
         <v>1</v>
@@ -3352,16 +3355,16 @@
         <v>31</v>
       </c>
       <c r="B164">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C164" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D164" t="b">
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
@@ -3369,16 +3372,16 @@
         <v>31</v>
       </c>
       <c r="B165">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D165" t="b">
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -3386,16 +3389,16 @@
         <v>31</v>
       </c>
       <c r="B166">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C166" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D166" t="b">
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -3403,16 +3406,16 @@
         <v>31</v>
       </c>
       <c r="B167">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C167" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D167" t="b">
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -3420,10 +3423,10 @@
         <v>31</v>
       </c>
       <c r="B168">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C168" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D168" t="b">
         <v>1</v>
@@ -3437,16 +3440,16 @@
         <v>31</v>
       </c>
       <c r="B169">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C169" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D169" t="b">
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -3454,10 +3457,10 @@
         <v>31</v>
       </c>
       <c r="B170">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C170" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D170" t="b">
         <v>1</v>
@@ -3471,27 +3474,27 @@
         <v>31</v>
       </c>
       <c r="B171">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C171" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D171" t="b">
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B172">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C172" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D172" t="b">
         <v>1</v>
@@ -3502,13 +3505,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B173">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C173" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D173" t="b">
         <v>1</v>
@@ -3519,13 +3522,13 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B174">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C174" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D174" t="b">
         <v>1</v>
@@ -3536,13 +3539,13 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B175">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C175" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D175" t="b">
         <v>1</v>
@@ -3553,13 +3556,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B176">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C176" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D176" t="b">
         <v>1</v>
@@ -3570,13 +3573,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B177">
         <v>2012</v>
       </c>
       <c r="C177" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D177" t="b">
         <v>1</v>
@@ -3587,13 +3590,13 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B178">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C178" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D178" t="b">
         <v>1</v>
@@ -3604,13 +3607,13 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B179">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C179" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D179" t="b">
         <v>1</v>
@@ -3624,10 +3627,10 @@
         <v>33</v>
       </c>
       <c r="B180">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="C180" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D180" t="b">
         <v>1</v>
@@ -3641,10 +3644,10 @@
         <v>33</v>
       </c>
       <c r="B181">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D181" t="b">
         <v>1</v>
@@ -3658,10 +3661,10 @@
         <v>33</v>
       </c>
       <c r="B182">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D182" t="b">
         <v>1</v>
@@ -3675,7 +3678,7 @@
         <v>33</v>
       </c>
       <c r="B183">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C183" t="s">
         <v>8</v>
@@ -3689,13 +3692,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B184">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C184" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D184" t="b">
         <v>1</v>
@@ -3706,13 +3709,13 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B185">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C185" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D185" t="b">
         <v>1</v>
@@ -3723,13 +3726,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B186">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C186" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D186" t="b">
         <v>1</v>
@@ -3740,10 +3743,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B187">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C187" t="s">
         <v>8</v>
@@ -3760,10 +3763,10 @@
         <v>34</v>
       </c>
       <c r="B188">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="C188" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D188" t="b">
         <v>1</v>
@@ -3777,10 +3780,10 @@
         <v>34</v>
       </c>
       <c r="B189">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C189" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D189" t="b">
         <v>1</v>
@@ -3791,13 +3794,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B190">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C190" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D190" t="b">
         <v>1</v>
@@ -3808,10 +3811,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B191">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C191" t="s">
         <v>8</v>
@@ -3825,10 +3828,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B192">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C192" t="s">
         <v>9</v>
@@ -3842,10 +3845,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B193">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C193" t="s">
         <v>10</v>
@@ -3862,7 +3865,7 @@
         <v>35</v>
       </c>
       <c r="B194">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C194" t="s">
         <v>6</v>
@@ -3879,7 +3882,7 @@
         <v>35</v>
       </c>
       <c r="B195">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
@@ -3896,7 +3899,7 @@
         <v>35</v>
       </c>
       <c r="B196">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C196" t="s">
         <v>9</v>
@@ -3913,7 +3916,7 @@
         <v>35</v>
       </c>
       <c r="B197">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C197" t="s">
         <v>10</v>
@@ -3930,7 +3933,7 @@
         <v>35</v>
       </c>
       <c r="B198">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C198" t="s">
         <v>6</v>
@@ -3947,7 +3950,7 @@
         <v>35</v>
       </c>
       <c r="B199">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C199" t="s">
         <v>8</v>
@@ -3964,7 +3967,7 @@
         <v>35</v>
       </c>
       <c r="B200">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C200" t="s">
         <v>9</v>
@@ -3981,7 +3984,7 @@
         <v>35</v>
       </c>
       <c r="B201">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C201" t="s">
         <v>10</v>
@@ -3998,7 +4001,7 @@
         <v>35</v>
       </c>
       <c r="B202">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C202" t="s">
         <v>6</v>
@@ -4015,7 +4018,7 @@
         <v>35</v>
       </c>
       <c r="B203">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C203" t="s">
         <v>8</v>
@@ -4032,7 +4035,7 @@
         <v>35</v>
       </c>
       <c r="B204">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C204" t="s">
         <v>9</v>
@@ -4049,7 +4052,7 @@
         <v>35</v>
       </c>
       <c r="B205">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C205" t="s">
         <v>10</v>
@@ -4066,7 +4069,7 @@
         <v>35</v>
       </c>
       <c r="B206">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C206" t="s">
         <v>6</v>
@@ -4083,7 +4086,7 @@
         <v>35</v>
       </c>
       <c r="B207">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C207" t="s">
         <v>8</v>
@@ -4100,10 +4103,10 @@
         <v>35</v>
       </c>
       <c r="B208">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C208" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D208" t="b">
         <v>1</v>
@@ -4117,10 +4120,10 @@
         <v>35</v>
       </c>
       <c r="B209">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C209" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D209" t="b">
         <v>1</v>
@@ -4131,13 +4134,13 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B210">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C210" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D210" t="b">
         <v>1</v>
@@ -4148,13 +4151,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B211">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C211" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D211" t="b">
         <v>1</v>
@@ -4165,13 +4168,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B212">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C212" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D212" t="b">
         <v>1</v>
@@ -4182,13 +4185,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B213">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C213" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D213" t="b">
         <v>1</v>
@@ -4199,7 +4202,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B214">
         <v>2010</v>
@@ -4216,7 +4219,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B215">
         <v>2010</v>
@@ -4233,7 +4236,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B216">
         <v>2014</v>
@@ -4250,7 +4253,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B217">
         <v>2014</v>
@@ -4267,30 +4270,30 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B218">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C218" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D218" t="b">
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B219">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="C219" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D219" t="b">
         <v>1</v>
@@ -4301,30 +4304,30 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B220">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C220" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D220" t="b">
         <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B221">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C221" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D221" t="b">
         <v>1</v>
@@ -4338,16 +4341,16 @@
         <v>38</v>
       </c>
       <c r="B222">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C222" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D222" t="b">
         <v>1</v>
       </c>
       <c r="E222" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
@@ -4355,7 +4358,7 @@
         <v>38</v>
       </c>
       <c r="B223">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C223" t="s">
         <v>6</v>
@@ -4372,7 +4375,7 @@
         <v>38</v>
       </c>
       <c r="B224">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C224" t="s">
         <v>6</v>
@@ -4389,7 +4392,7 @@
         <v>38</v>
       </c>
       <c r="B225">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C225" t="s">
         <v>9</v>
@@ -4406,7 +4409,7 @@
         <v>38</v>
       </c>
       <c r="B226">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C226" t="s">
         <v>10</v>
@@ -4423,7 +4426,7 @@
         <v>38</v>
       </c>
       <c r="B227">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C227" t="s">
         <v>6</v>
@@ -4440,7 +4443,7 @@
         <v>38</v>
       </c>
       <c r="B228">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C228" t="s">
         <v>6</v>
@@ -4457,10 +4460,10 @@
         <v>38</v>
       </c>
       <c r="B229">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C229" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D229" t="b">
         <v>1</v>
@@ -4474,27 +4477,27 @@
         <v>38</v>
       </c>
       <c r="B230">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C230" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D230" t="b">
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B231">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C231" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D231" t="b">
         <v>1</v>
@@ -4505,30 +4508,30 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B232">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C232" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B233">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C233" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D233" t="b">
         <v>1</v>
@@ -4539,27 +4542,27 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B234">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C234" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
       </c>
       <c r="E234" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B235">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C235" t="s">
         <v>9</v>
@@ -4568,15 +4571,15 @@
         <v>1</v>
       </c>
       <c r="E235" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B236">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C236" t="s">
         <v>10</v>
@@ -4590,10 +4593,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B237">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C237" t="s">
         <v>9</v>
@@ -4602,15 +4605,15 @@
         <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B238">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C238" t="s">
         <v>10</v>
@@ -4627,7 +4630,7 @@
         <v>41</v>
       </c>
       <c r="B239">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C239" t="s">
         <v>9</v>
@@ -4644,7 +4647,7 @@
         <v>41</v>
       </c>
       <c r="B240">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C240" t="s">
         <v>10</v>
@@ -4661,7 +4664,7 @@
         <v>41</v>
       </c>
       <c r="B241">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C241" t="s">
         <v>9</v>
@@ -4678,7 +4681,7 @@
         <v>41</v>
       </c>
       <c r="B242">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C242" t="s">
         <v>10</v>
@@ -4695,7 +4698,7 @@
         <v>41</v>
       </c>
       <c r="B243">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C243" t="s">
         <v>9</v>
@@ -4712,7 +4715,7 @@
         <v>41</v>
       </c>
       <c r="B244">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C244" t="s">
         <v>10</v>
@@ -4726,30 +4729,30 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B245">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C245" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D245" t="b">
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B246">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C246" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D246" t="b">
         <v>1</v>
@@ -4760,10 +4763,10 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B247">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C247" t="s">
         <v>9</v>
@@ -4777,10 +4780,10 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B248">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C248" t="s">
         <v>10</v>
@@ -4789,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="E248" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
@@ -4797,7 +4800,7 @@
         <v>42</v>
       </c>
       <c r="B249">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C249" t="s">
         <v>6</v>
@@ -4814,7 +4817,7 @@
         <v>42</v>
       </c>
       <c r="B250">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C250" t="s">
         <v>8</v>
@@ -4831,7 +4834,7 @@
         <v>42</v>
       </c>
       <c r="B251">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C251" t="s">
         <v>9</v>
@@ -4848,7 +4851,7 @@
         <v>42</v>
       </c>
       <c r="B252">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C252" t="s">
         <v>10</v>
@@ -4865,7 +4868,7 @@
         <v>42</v>
       </c>
       <c r="B253">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C253" t="s">
         <v>6</v>
@@ -4882,7 +4885,7 @@
         <v>42</v>
       </c>
       <c r="B254">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C254" t="s">
         <v>8</v>
@@ -4899,7 +4902,7 @@
         <v>42</v>
       </c>
       <c r="B255">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C255" t="s">
         <v>9</v>
@@ -4916,7 +4919,7 @@
         <v>42</v>
       </c>
       <c r="B256">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C256" t="s">
         <v>10</v>
@@ -4933,7 +4936,7 @@
         <v>42</v>
       </c>
       <c r="B257">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C257" t="s">
         <v>6</v>
@@ -4950,7 +4953,7 @@
         <v>42</v>
       </c>
       <c r="B258">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C258" t="s">
         <v>8</v>
@@ -4967,7 +4970,7 @@
         <v>42</v>
       </c>
       <c r="B259">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C259" t="s">
         <v>9</v>
@@ -4984,7 +4987,7 @@
         <v>42</v>
       </c>
       <c r="B260">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C260" t="s">
         <v>10</v>
@@ -5001,7 +5004,7 @@
         <v>42</v>
       </c>
       <c r="B261">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C261" t="s">
         <v>6</v>
@@ -5018,7 +5021,7 @@
         <v>42</v>
       </c>
       <c r="B262">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C262" t="s">
         <v>8</v>
@@ -5032,47 +5035,47 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B263">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C263" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D263" t="b">
         <v>1</v>
       </c>
       <c r="E263" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B264">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C264" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D264" t="b">
         <v>1</v>
       </c>
       <c r="E264" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B265">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C265" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D265" t="b">
         <v>1</v>
@@ -5083,10 +5086,10 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B266">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C266" t="s">
         <v>8</v>
@@ -5103,10 +5106,10 @@
         <v>43</v>
       </c>
       <c r="B267">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C267" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D267" t="b">
         <v>1</v>
@@ -5120,10 +5123,10 @@
         <v>43</v>
       </c>
       <c r="B268">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C268" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D268" t="b">
         <v>1</v>
@@ -5137,10 +5140,10 @@
         <v>43</v>
       </c>
       <c r="B269">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C269" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D269" t="b">
         <v>1</v>
@@ -5151,47 +5154,47 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B270">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C270" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D270" t="b">
         <v>1</v>
       </c>
       <c r="E270" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B271">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C271" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D271" t="b">
         <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B272">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C272" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D272" t="b">
         <v>1</v>
@@ -5202,19 +5205,19 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B273">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C273" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D273" t="b">
         <v>1</v>
       </c>
       <c r="E273" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
@@ -5222,7 +5225,7 @@
         <v>44</v>
       </c>
       <c r="B274">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C274" t="s">
         <v>10</v>
@@ -5239,16 +5242,16 @@
         <v>44</v>
       </c>
       <c r="B275">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C275" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D275" t="b">
         <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
@@ -5256,16 +5259,16 @@
         <v>44</v>
       </c>
       <c r="B276">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C276" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D276" t="b">
         <v>1</v>
       </c>
       <c r="E276" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
@@ -5273,7 +5276,7 @@
         <v>44</v>
       </c>
       <c r="B277">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C277" t="s">
         <v>10</v>
@@ -5287,30 +5290,30 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B278">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C278" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D278" t="b">
         <v>1</v>
       </c>
       <c r="E278" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B279">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C279" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D279" t="b">
         <v>1</v>
@@ -5321,36 +5324,36 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B280">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C280" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D280" t="b">
         <v>1</v>
       </c>
       <c r="E280" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B281">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C281" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D281" t="b">
         <v>1</v>
       </c>
       <c r="E281" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
@@ -5358,10 +5361,10 @@
         <v>45</v>
       </c>
       <c r="B282">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C282" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D282" t="b">
         <v>1</v>
@@ -5372,13 +5375,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B283">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C283" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D283" t="b">
         <v>1</v>
@@ -5389,13 +5392,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B284">
         <v>2012</v>
       </c>
       <c r="C284" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D284" t="b">
         <v>1</v>
@@ -5406,10 +5409,10 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B285">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C285" t="s">
         <v>9</v>
@@ -5423,10 +5426,10 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B286">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C286" t="s">
         <v>10</v>
@@ -5440,7 +5443,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B287">
         <v>2012</v>
@@ -5457,7 +5460,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B288">
         <v>2012</v>
@@ -5474,7 +5477,7 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B289">
         <v>2016</v>
@@ -5491,7 +5494,7 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B290">
         <v>2016</v>
@@ -5508,30 +5511,30 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B291">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C291" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D291" t="b">
         <v>1</v>
       </c>
       <c r="E291" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B292">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C292" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D292" t="b">
         <v>1</v>
@@ -5542,30 +5545,30 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B293">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C293" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D293" t="b">
         <v>1</v>
       </c>
       <c r="E293" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B294">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C294" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D294" t="b">
         <v>1</v>
@@ -5579,7 +5582,7 @@
         <v>48</v>
       </c>
       <c r="B295">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C295" t="s">
         <v>10</v>
@@ -5588,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="E295" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
@@ -5596,16 +5599,16 @@
         <v>48</v>
       </c>
       <c r="B296">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C296" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D296" t="b">
         <v>1</v>
       </c>
       <c r="E296" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
@@ -5613,7 +5616,7 @@
         <v>48</v>
       </c>
       <c r="B297">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C297" t="s">
         <v>10</v>
@@ -5630,7 +5633,7 @@
         <v>48</v>
       </c>
       <c r="B298">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C298" t="s">
         <v>9</v>
@@ -5647,7 +5650,7 @@
         <v>48</v>
       </c>
       <c r="B299">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C299" t="s">
         <v>10</v>
@@ -5661,10 +5664,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B300">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C300" t="s">
         <v>9</v>
@@ -5673,15 +5676,15 @@
         <v>1</v>
       </c>
       <c r="E300" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B301">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C301" t="s">
         <v>10</v>
@@ -5690,15 +5693,15 @@
         <v>1</v>
       </c>
       <c r="E301" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B302">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C302" t="s">
         <v>9</v>
@@ -5712,10 +5715,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B303">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C303" t="s">
         <v>10</v>
@@ -5732,7 +5735,7 @@
         <v>49</v>
       </c>
       <c r="B304">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C304" t="s">
         <v>9</v>
@@ -5749,7 +5752,7 @@
         <v>49</v>
       </c>
       <c r="B305">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C305" t="s">
         <v>10</v>
@@ -5763,10 +5766,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B306">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C306" t="s">
         <v>9</v>
@@ -5780,10 +5783,10 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B307">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C307" t="s">
         <v>10</v>
@@ -5792,15 +5795,15 @@
         <v>1</v>
       </c>
       <c r="E307" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B308">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C308" t="s">
         <v>9</v>
@@ -5814,10 +5817,10 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B309">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C309" t="s">
         <v>10</v>
@@ -5826,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
@@ -5834,7 +5837,7 @@
         <v>50</v>
       </c>
       <c r="B310">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C310" t="s">
         <v>9</v>
@@ -5851,7 +5854,7 @@
         <v>50</v>
       </c>
       <c r="B311">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C311" t="s">
         <v>10</v>
@@ -5865,10 +5868,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B312">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C312" t="s">
         <v>9</v>
@@ -5882,10 +5885,10 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B313">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C313" t="s">
         <v>10</v>
@@ -5894,15 +5897,15 @@
         <v>1</v>
       </c>
       <c r="E313" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B314">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C314" t="s">
         <v>9</v>
@@ -5916,10 +5919,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B315">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C315" t="s">
         <v>10</v>
@@ -5928,18 +5931,18 @@
         <v>1</v>
       </c>
       <c r="E315" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B316">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C316" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D316" t="b">
         <v>1</v>
@@ -5950,13 +5953,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B317">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C317" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D317" t="b">
         <v>1</v>
@@ -5967,10 +5970,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B318">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C318" t="s">
         <v>9</v>
@@ -5984,10 +5987,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B319">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C319" t="s">
         <v>10</v>
@@ -6004,10 +6007,10 @@
         <v>52</v>
       </c>
       <c r="B320">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C320" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D320" t="b">
         <v>1</v>
@@ -6021,10 +6024,10 @@
         <v>52</v>
       </c>
       <c r="B321">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C321" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D321" t="b">
         <v>1</v>
@@ -6035,7 +6038,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B322">
         <v>2012</v>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B323">
         <v>2012</v>
@@ -6069,7 +6072,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B324">
         <v>2016</v>
@@ -6086,7 +6089,7 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B325">
         <v>2016</v>
@@ -6103,10 +6106,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B326">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C326" t="s">
         <v>9</v>
@@ -6115,15 +6118,15 @@
         <v>1</v>
       </c>
       <c r="E326" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B327">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C327" t="s">
         <v>10</v>
@@ -6132,15 +6135,15 @@
         <v>1</v>
       </c>
       <c r="E327" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B328">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C328" t="s">
         <v>9</v>
@@ -6149,15 +6152,15 @@
         <v>1</v>
       </c>
       <c r="E328" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B329">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C329" t="s">
         <v>10</v>
@@ -6166,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="E329" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
@@ -6174,7 +6177,7 @@
         <v>54</v>
       </c>
       <c r="B330">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C330" t="s">
         <v>9</v>
@@ -6191,7 +6194,7 @@
         <v>54</v>
       </c>
       <c r="B331">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C331" t="s">
         <v>10</v>
@@ -6208,7 +6211,7 @@
         <v>54</v>
       </c>
       <c r="B332">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C332" t="s">
         <v>9</v>
@@ -6225,7 +6228,7 @@
         <v>54</v>
       </c>
       <c r="B333">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C333" t="s">
         <v>10</v>
@@ -6242,7 +6245,7 @@
         <v>54</v>
       </c>
       <c r="B334">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C334" t="s">
         <v>9</v>
@@ -6259,7 +6262,7 @@
         <v>54</v>
       </c>
       <c r="B335">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C335" t="s">
         <v>10</v>
@@ -6273,13 +6276,13 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B336">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C336" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D336" t="b">
         <v>1</v>
@@ -6290,10 +6293,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B337">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C337" t="s">
         <v>10</v>
@@ -6307,10 +6310,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B338">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C338" t="s">
         <v>9</v>
@@ -6319,15 +6322,15 @@
         <v>1</v>
       </c>
       <c r="E338" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B339">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C339" t="s">
         <v>10</v>
@@ -6336,7 +6339,7 @@
         <v>1</v>
       </c>
       <c r="E339" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
@@ -6344,7 +6347,7 @@
         <v>55</v>
       </c>
       <c r="B340">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C340" t="s">
         <v>10</v>
@@ -6361,16 +6364,16 @@
         <v>55</v>
       </c>
       <c r="B341">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C341" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D341" t="b">
         <v>1</v>
       </c>
       <c r="E341" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
@@ -6378,10 +6381,10 @@
         <v>55</v>
       </c>
       <c r="B342">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C342" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D342" t="b">
         <v>1</v>
@@ -6392,10 +6395,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B343">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C343" t="s">
         <v>10</v>
@@ -6404,15 +6407,15 @@
         <v>1</v>
       </c>
       <c r="E343" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B344">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C344" t="s">
         <v>10</v>
@@ -6426,24 +6429,24 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B345">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C345" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D345" t="b">
         <v>1</v>
       </c>
       <c r="E345" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B346">
         <v>2016</v>
@@ -6455,7 +6458,7 @@
         <v>1</v>
       </c>
       <c r="E346" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
@@ -6463,7 +6466,7 @@
         <v>56</v>
       </c>
       <c r="B347">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C347" t="s">
         <v>10</v>
@@ -6480,7 +6483,7 @@
         <v>56</v>
       </c>
       <c r="B348">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C348" t="s">
         <v>10</v>
@@ -6497,7 +6500,7 @@
         <v>56</v>
       </c>
       <c r="B349">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C349" t="s">
         <v>10</v>
@@ -6514,78 +6517,78 @@
         <v>56</v>
       </c>
       <c r="B350">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C350" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D350" t="b">
         <v>1</v>
       </c>
       <c r="E350" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B351">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C351" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D351" t="b">
         <v>1</v>
       </c>
       <c r="E351" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B352">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C352" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D352" t="b">
         <v>1</v>
       </c>
       <c r="E352" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B353">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C353" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D353" t="b">
         <v>1</v>
       </c>
       <c r="E353" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B354">
         <v>2010</v>
       </c>
       <c r="C354" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D354" t="b">
         <v>1</v>
@@ -6599,7 +6602,7 @@
         <v>57</v>
       </c>
       <c r="B355">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C355" t="s">
         <v>6</v>
@@ -6616,7 +6619,7 @@
         <v>57</v>
       </c>
       <c r="B356">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C356" t="s">
         <v>8</v>
@@ -6633,7 +6636,7 @@
         <v>57</v>
       </c>
       <c r="B357">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C357" t="s">
         <v>9</v>
@@ -6650,7 +6653,7 @@
         <v>57</v>
       </c>
       <c r="B358">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C358" t="s">
         <v>10</v>
@@ -6667,7 +6670,7 @@
         <v>57</v>
       </c>
       <c r="B359">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C359" t="s">
         <v>6</v>
@@ -6684,10 +6687,10 @@
         <v>57</v>
       </c>
       <c r="B360">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C360" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="D360" t="b">
         <v>1</v>
@@ -6704,7 +6707,7 @@
         <v>2012</v>
       </c>
       <c r="C361" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D361" t="b">
         <v>1</v>
@@ -6718,10 +6721,10 @@
         <v>57</v>
       </c>
       <c r="B362">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C362" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D362" t="b">
         <v>1</v>
@@ -6735,10 +6738,10 @@
         <v>57</v>
       </c>
       <c r="B363">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C363" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D363" t="b">
         <v>1</v>
@@ -6752,10 +6755,10 @@
         <v>57</v>
       </c>
       <c r="B364">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C364" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D364" t="b">
         <v>1</v>
@@ -6769,7 +6772,7 @@
         <v>57</v>
       </c>
       <c r="B365">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C365" t="s">
         <v>8</v>
@@ -6786,7 +6789,7 @@
         <v>57</v>
       </c>
       <c r="B366">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C366" t="s">
         <v>9</v>
@@ -6803,7 +6806,7 @@
         <v>57</v>
       </c>
       <c r="B367">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C367" t="s">
         <v>10</v>
@@ -6820,7 +6823,7 @@
         <v>57</v>
       </c>
       <c r="B368">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C368" t="s">
         <v>6</v>
@@ -6837,7 +6840,7 @@
         <v>57</v>
       </c>
       <c r="B369">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C369" t="s">
         <v>8</v>
@@ -6854,10 +6857,10 @@
         <v>57</v>
       </c>
       <c r="B370">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C370" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D370" t="b">
         <v>1</v>
@@ -6871,10 +6874,10 @@
         <v>57</v>
       </c>
       <c r="B371">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C371" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D371" t="b">
         <v>1</v>
@@ -6888,10 +6891,10 @@
         <v>57</v>
       </c>
       <c r="B372">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C372" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D372" t="b">
         <v>1</v>
@@ -6902,13 +6905,13 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B373">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C373" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D373" t="b">
         <v>1</v>
@@ -6919,13 +6922,13 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B374">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C374" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D374" t="b">
         <v>1</v>
@@ -6936,13 +6939,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B375">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C375" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D375" t="b">
         <v>1</v>
@@ -6953,13 +6956,13 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B376">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C376" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D376" t="b">
         <v>1</v>
@@ -6973,7 +6976,7 @@
         <v>58</v>
       </c>
       <c r="B377">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="C377" t="s">
         <v>9</v>
@@ -6987,13 +6990,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B378">
         <v>2010</v>
       </c>
       <c r="C378" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D378" t="b">
         <v>1</v>
@@ -7004,13 +7007,13 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B379">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C379" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D379" t="b">
         <v>1</v>
@@ -7021,13 +7024,13 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B380">
         <v>2014</v>
       </c>
       <c r="C380" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D380" t="b">
         <v>1</v>
@@ -7038,13 +7041,13 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B381">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C381" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D381" t="b">
         <v>1</v>
@@ -7055,10 +7058,10 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B382">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C382" t="s">
         <v>9</v>
@@ -7072,10 +7075,10 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B383">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C383" t="s">
         <v>10</v>
@@ -7089,10 +7092,10 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B384">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C384" t="s">
         <v>9</v>
@@ -7106,10 +7109,10 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B385">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C385" t="s">
         <v>10</v>
@@ -7123,10 +7126,10 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B386">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C386" t="s">
         <v>9</v>
@@ -7135,32 +7138,32 @@
         <v>1</v>
       </c>
       <c r="E386" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B387">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C387" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D387" t="b">
         <v>1</v>
       </c>
       <c r="E387" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B388">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C388" t="s">
         <v>9</v>
@@ -7169,15 +7172,15 @@
         <v>1</v>
       </c>
       <c r="E388" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B389">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C389" t="s">
         <v>10</v>
@@ -7194,7 +7197,7 @@
         <v>61</v>
       </c>
       <c r="B390">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C390" t="s">
         <v>9</v>
@@ -7211,7 +7214,7 @@
         <v>61</v>
       </c>
       <c r="B391">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C391" t="s">
         <v>9</v>
@@ -7228,21 +7231,21 @@
         <v>61</v>
       </c>
       <c r="B392">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C392" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D392" t="b">
         <v>1</v>
       </c>
       <c r="E392" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B393">
         <v>2012</v>
@@ -7254,23 +7257,91 @@
         <v>1</v>
       </c>
       <c r="E393" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
+        <v>61</v>
+      </c>
+      <c r="B394">
+        <v>2014</v>
+      </c>
+      <c r="C394" t="s">
+        <v>9</v>
+      </c>
+      <c r="D394" t="b">
+        <v>1</v>
+      </c>
+      <c r="E394" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>61</v>
+      </c>
+      <c r="B395">
+        <v>2016</v>
+      </c>
+      <c r="C395" t="s">
+        <v>9</v>
+      </c>
+      <c r="D395" t="b">
+        <v>1</v>
+      </c>
+      <c r="E395" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>61</v>
+      </c>
+      <c r="B396">
+        <v>2016</v>
+      </c>
+      <c r="C396" t="s">
+        <v>10</v>
+      </c>
+      <c r="D396" t="b">
+        <v>1</v>
+      </c>
+      <c r="E396" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
         <v>50</v>
       </c>
-      <c r="B394">
-        <v>2016</v>
-      </c>
-      <c r="C394" t="s">
-        <v>10</v>
-      </c>
-      <c r="D394" t="b">
-        <v>1</v>
-      </c>
-      <c r="E394" t="s">
+      <c r="B397">
+        <v>2012</v>
+      </c>
+      <c r="C397" t="s">
+        <v>10</v>
+      </c>
+      <c r="D397" t="b">
+        <v>1</v>
+      </c>
+      <c r="E397" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>50</v>
+      </c>
+      <c r="B398">
+        <v>2016</v>
+      </c>
+      <c r="C398" t="s">
+        <v>10</v>
+      </c>
+      <c r="D398" t="b">
+        <v>1</v>
+      </c>
+      <c r="E398" t="s">
         <v>12</v>
       </c>
     </row>
